--- a/runs/exp8_final/beautified_exam_schedule.xlsx
+++ b/runs/exp8_final/beautified_exam_schedule.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/runs/exp8_final/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_42655B9F120D3DDA63169890BF2B360379785166" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0892399E-0454-40C7-9193-60E60CC0DFB8}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="378">
   <si>
     <t>Day</t>
   </si>
@@ -1145,13 +1151,16 @@
   </si>
   <si>
     <t>BM CSE 483(32:4)</t>
+  </si>
+  <si>
+    <t>Ylab-3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1224,7 +1233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1247,11 +1256,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1259,26 +1279,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1316,7 +1351,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1350,6 +1385,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1384,9 +1420,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1559,15 +1596,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE82"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF82"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="31" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="2" max="31" width="16.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1661,60 +1698,63 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" s="2" customFormat="1">
-      <c r="A2" s="2" t="s">
+      <c r="AF1" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>69</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>78</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="11" t="s">
         <v>272</v>
       </c>
       <c r="X2" s="7" t="s">
@@ -1723,262 +1763,262 @@
       <c r="Y2" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AB2" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AC2" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AD2" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AE2" s="8" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="3"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="8"/>
+      <c r="I3" s="9"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="6"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="11"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
-      <c r="Z3" s="3"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-    </row>
-    <row r="4" spans="1:31" s="2" customFormat="1">
-      <c r="A4" s="2" t="s">
+      <c r="Z3" s="5"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+    </row>
+    <row r="4" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AA4" s="10" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="2" customFormat="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="9"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="6"/>
-      <c r="AA5" s="9"/>
-    </row>
-    <row r="6" spans="1:31" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
+      <c r="C5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="10"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="11"/>
+      <c r="AA5" s="10"/>
+    </row>
+    <row r="6" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="U7" s="9" t="s">
+      <c r="U7" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="X7" s="5" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="2" customFormat="1">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="G8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="6"/>
-      <c r="U8" s="9"/>
-      <c r="X8" s="3"/>
-    </row>
-    <row r="9" spans="1:31" s="2" customFormat="1">
-      <c r="A9" s="2" t="s">
+      <c r="E8" s="10"/>
+      <c r="G8" s="6"/>
+      <c r="L8" s="11"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="11"/>
+      <c r="U8" s="10"/>
+      <c r="X8" s="5"/>
+    </row>
+    <row r="9" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="Q9" s="5" t="s">
+      <c r="Q9" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="R9" s="5" t="s">
+      <c r="R9" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="S9" s="5" t="s">
+      <c r="S9" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="U9" s="5" t="s">
+      <c r="U9" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="AA9" s="5" t="s">
+      <c r="AA9" s="6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="2" customFormat="1">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="AA10" s="5"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" t="s">
+      <c r="I10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="AA10" s="6"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>102</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="O11" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="8" t="s">
         <v>210</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="T11" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="U11" s="3" t="s">
+      <c r="U11" s="5" t="s">
         <v>275</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="X11" s="3" t="s">
+      <c r="X11" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="Y11" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="Z11" s="3" t="s">
+      <c r="Z11" s="5" t="s">
         <v>329</v>
       </c>
       <c r="AA11" s="7" t="s">
@@ -1988,416 +2028,416 @@
         <v>364</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
-      <c r="A12" t="s">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="3"/>
-      <c r="G12" s="5" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="5"/>
+      <c r="G12" s="6" t="s">
         <v>71</v>
       </c>
       <c r="H12" s="7"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="8"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="9"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="4"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="4"/>
+      <c r="L12" s="8"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="8"/>
       <c r="R12" s="7"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="3"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="5"/>
       <c r="V12" s="7"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
       <c r="AA12" s="7"/>
       <c r="AD12" s="7"/>
     </row>
-    <row r="13" spans="1:31">
-      <c r="A13" t="s">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="I13" s="9" t="s">
+      <c r="G13" s="6"/>
+      <c r="I13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="O13" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="P13" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="10" t="s">
         <v>82</v>
       </c>
       <c r="R13" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="V13" s="6" t="s">
+      <c r="V13" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Y13" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="Z13" s="8" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
-      <c r="A14" t="s">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="I14" s="9"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
       <c r="R14" s="7"/>
-      <c r="V14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="4"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="A15" t="s">
+      <c r="V14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="8"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A15" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
-      <c r="A16" t="s">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="N16" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O16" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="P16" s="5" t="s">
+      <c r="P16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="Q16" s="5" t="s">
+      <c r="Q16" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="5" t="s">
+      <c r="R16" s="6" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
-      <c r="A17" t="s">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="1:31">
-      <c r="A18" t="s">
+      <c r="I17" s="9"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="O18" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="P18" s="5" t="s">
+      <c r="P18" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="V18" s="8" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
-      <c r="A19" t="s">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="V19" s="4"/>
-    </row>
-    <row r="20" spans="1:31" s="2" customFormat="1">
-      <c r="A20" s="2" t="s">
+      <c r="I19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="V19" s="8"/>
+    </row>
+    <row r="20" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="N20" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="O20" s="9" t="s">
+      <c r="O20" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="P20" s="8" t="s">
+      <c r="P20" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="R20" s="5" t="s">
+      <c r="R20" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="T20" s="3" t="s">
+      <c r="T20" s="5" t="s">
         <v>269</v>
       </c>
       <c r="U20" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="V20" s="8" t="s">
+      <c r="V20" s="9" t="s">
         <v>286</v>
       </c>
       <c r="W20" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="X20" s="9" t="s">
+      <c r="X20" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="AA20" s="3" t="s">
+      <c r="AA20" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AB20" s="4" t="s">
+      <c r="AB20" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="AC20" s="4" t="s">
+      <c r="AC20" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="AE20" s="4" t="s">
+      <c r="AE20" s="8" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="21" spans="1:31" s="2" customFormat="1">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="K21" s="3"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="5"/>
-      <c r="T21" s="3"/>
+      <c r="E21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="K21" s="5"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="6"/>
+      <c r="T21" s="5"/>
       <c r="U21" s="7"/>
-      <c r="V21" s="8"/>
+      <c r="V21" s="9"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="9"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
-      <c r="AE21" s="4"/>
-    </row>
-    <row r="22" spans="1:31" s="2" customFormat="1">
-      <c r="A22" s="2" t="s">
+      <c r="X21" s="10"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AE21" s="8"/>
+    </row>
+    <row r="22" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="6" t="s">
         <v>86</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="N22" s="5" t="s">
+      <c r="N22" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="O22" s="5" t="s">
+      <c r="O22" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="P22" s="6" t="s">
+      <c r="P22" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="Q22" s="5" t="s">
+      <c r="Q22" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="R22" s="5" t="s">
+      <c r="R22" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="U22" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="V22" s="8" t="s">
+      <c r="V22" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="AB22" s="4" t="s">
+      <c r="AB22" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="AC22" s="4" t="s">
+      <c r="AC22" s="8" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="23" spans="1:31" s="2" customFormat="1">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="5"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="6"/>
       <c r="K23" s="7"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-    </row>
-    <row r="24" spans="1:31" s="2" customFormat="1">
-      <c r="A24" s="2" t="s">
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8"/>
+    </row>
+    <row r="24" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:31" s="2" customFormat="1">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="N25" s="8" t="s">
+      <c r="N25" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="P25" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="Q25" s="6" t="s">
+      <c r="Q25" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="R25" s="6" t="s">
+      <c r="R25" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="AA25" s="5" t="s">
+      <c r="AA25" s="6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="2" customFormat="1">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="4"/>
-      <c r="K26" s="6"/>
-      <c r="N26" s="8"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="AA26" s="5"/>
-    </row>
-    <row r="27" spans="1:31" s="2" customFormat="1">
-      <c r="A27" s="2" t="s">
+      <c r="I26" s="8"/>
+      <c r="K26" s="11"/>
+      <c r="N26" s="9"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="AA26" s="6"/>
+    </row>
+    <row r="27" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="N27" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="P27" s="9" t="s">
+      <c r="P27" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="R27" s="9" t="s">
+      <c r="R27" s="10" t="s">
         <v>238</v>
       </c>
       <c r="Y27" s="7" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="2" customFormat="1">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="R28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="R28" s="10"/>
       <c r="Y28" s="7"/>
     </row>
-    <row r="29" spans="1:31">
-      <c r="A29" t="s">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="M29" s="9" t="s">
         <v>130</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="O29" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="P29" s="8" t="s">
+      <c r="P29" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="Q29" s="9" t="s">
+      <c r="Q29" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="R29" s="6" t="s">
+      <c r="R29" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="S29" s="5" t="s">
+      <c r="S29" s="6" t="s">
         <v>262</v>
       </c>
       <c r="T29" s="7" t="s">
@@ -2406,1173 +2446,1291 @@
       <c r="V29" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="X29" s="8" t="s">
+      <c r="X29" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="Y29" s="8" t="s">
+      <c r="Y29" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="AA29" s="3" t="s">
+      <c r="AA29" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="AD29" s="4" t="s">
+      <c r="AD29" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="AE29" s="4" t="s">
+      <c r="AE29" s="8" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
-      <c r="A30" t="s">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="10"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="3"/>
-      <c r="I30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="M30" s="8"/>
+      <c r="G30" s="5"/>
+      <c r="I30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="M30" s="9"/>
       <c r="N30" s="7"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="5"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="6"/>
       <c r="T30" s="7"/>
       <c r="V30" s="7"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="8"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-    </row>
-    <row r="31" spans="1:31">
-      <c r="A31" t="s">
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AD30" s="8"/>
+      <c r="AE30" s="8"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="O31" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="P31" s="9" t="s">
+      <c r="P31" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="R31" s="9" t="s">
+      <c r="R31" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="U31" s="6" t="s">
+      <c r="U31" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="AA31" s="9" t="s">
+      <c r="AA31" s="10" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
-      <c r="A32" t="s">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A32" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="D32" s="9"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="U32" s="6"/>
-      <c r="AA32" s="9"/>
-    </row>
-    <row r="33" spans="1:31">
-      <c r="A33" t="s">
+      <c r="B32" s="6"/>
+      <c r="D32" s="10"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="U32" s="11"/>
+      <c r="AA32" s="10"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A33" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
-      <c r="A34" t="s">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
-      <c r="A35" t="s">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
-      <c r="A36" t="s">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A36" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="P36" s="5" t="s">
+      <c r="P36" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="Q36" s="6" t="s">
+      <c r="Q36" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="R36" s="8" t="s">
+      <c r="R36" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="X36" s="5" t="s">
+      <c r="X36" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="Y36" s="9" t="s">
+      <c r="Y36" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="Z36" s="6" t="s">
+      <c r="Z36" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="AA36" s="6" t="s">
+      <c r="AA36" s="11" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
-      <c r="A37" t="s">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A37" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="8"/>
-      <c r="X37" s="5"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="6"/>
-    </row>
-    <row r="38" spans="1:31" s="2" customFormat="1">
-      <c r="A38" s="2" t="s">
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="9"/>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11"/>
+    </row>
+    <row r="38" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K38" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="L38" s="8" t="s">
+      <c r="L38" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="O38" s="9" t="s">
+      <c r="O38" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="P38" s="9" t="s">
+      <c r="P38" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="Q38" s="9" t="s">
+      <c r="Q38" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="R38" s="9" t="s">
+      <c r="R38" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="U38" s="8" t="s">
+      <c r="U38" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="V38" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="W38" s="8" t="s">
+      <c r="W38" s="9" t="s">
         <v>297</v>
       </c>
       <c r="X38" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="Y38" s="6" t="s">
+      <c r="Y38" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="Z38" s="3" t="s">
+      <c r="Z38" s="5" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="2" customFormat="1">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B39" s="7"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="F39" s="8"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="8"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="8"/>
-      <c r="W39" s="8"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="F39" s="9"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="9"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
       <c r="X39" s="7"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="1:31" s="2" customFormat="1">
-      <c r="A40" s="2" t="s">
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="5"/>
+    </row>
+    <row r="40" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K40" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="L40" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="O40" s="3" t="s">
+      <c r="O40" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="P40" s="3" t="s">
+      <c r="P40" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="Q40" s="6" t="s">
+      <c r="Q40" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="R40" s="4" t="s">
+      <c r="R40" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="V40" s="4" t="s">
+      <c r="V40" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="W40" s="3" t="s">
+      <c r="W40" s="5" t="s">
         <v>298</v>
       </c>
       <c r="X40" s="7" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="1:31" s="2" customFormat="1">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="I41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="5"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="3"/>
+      <c r="D41" s="11"/>
+      <c r="I41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="8"/>
+      <c r="V41" s="8"/>
+      <c r="W41" s="5"/>
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="1:31" s="2" customFormat="1">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:31" s="2" customFormat="1">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:31" s="2" customFormat="1">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H44" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="L44" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="O44" s="6" t="s">
+      <c r="O44" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="P44" s="9" t="s">
+      <c r="P44" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="Q44" s="9" t="s">
+      <c r="Q44" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="R44" s="6" t="s">
+      <c r="R44" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="V44" s="9" t="s">
+      <c r="V44" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="Y44" s="9" t="s">
+      <c r="Y44" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="AA44" s="5" t="s">
+      <c r="AA44" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="AD44" s="5" t="s">
+      <c r="AD44" s="6" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="2" customFormat="1">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="5"/>
-      <c r="L45" s="9"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="6"/>
-      <c r="V45" s="9"/>
-      <c r="Y45" s="9"/>
-      <c r="AA45" s="5"/>
-      <c r="AD45" s="5"/>
-    </row>
-    <row r="46" spans="1:31" s="2" customFormat="1">
-      <c r="A46" s="2" t="s">
+      <c r="C45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="6"/>
+      <c r="L45" s="10"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="11"/>
+      <c r="V45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="AA45" s="6"/>
+      <c r="AD45" s="6"/>
+    </row>
+    <row r="46" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
-      <c r="A47" t="s">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A47" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="9" t="s">
         <v>93</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="O47" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="P47" s="8" t="s">
+      <c r="P47" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="Q47" s="3" t="s">
+      <c r="Q47" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="R47" s="8" t="s">
+      <c r="R47" s="9" t="s">
         <v>245</v>
       </c>
       <c r="V47" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="W47" s="3" t="s">
+      <c r="W47" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="Y47" s="6" t="s">
+      <c r="Y47" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="AA47" s="5" t="s">
+      <c r="AA47" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="AC47" s="4" t="s">
+      <c r="AC47" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="AE47" s="4" t="s">
+      <c r="AE47" s="8" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
-      <c r="A48" t="s">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A48" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="6"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="8"/>
+      <c r="F48" s="11"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="9"/>
       <c r="J48" s="7"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="8"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="9"/>
       <c r="V48" s="7"/>
-      <c r="W48" s="3"/>
-      <c r="Y48" s="6"/>
-      <c r="AA48" s="5"/>
-      <c r="AC48" s="4"/>
-      <c r="AE48" s="4"/>
-    </row>
-    <row r="49" spans="1:31">
-      <c r="A49" t="s">
+      <c r="W48" s="5"/>
+      <c r="Y48" s="11"/>
+      <c r="AA48" s="6"/>
+      <c r="AC48" s="8"/>
+      <c r="AE48" s="8"/>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A49" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="L49" s="6" t="s">
+      <c r="L49" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="O49" s="9" t="s">
+      <c r="O49" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="P49" s="9" t="s">
+      <c r="P49" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="Q49" s="9" t="s">
+      <c r="Q49" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="R49" s="5" t="s">
+      <c r="R49" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="W49" s="6" t="s">
+      <c r="W49" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="Z49" s="5" t="s">
+      <c r="Z49" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="AA49" s="6" t="s">
+      <c r="AA49" s="11" t="s">
         <v>346</v>
       </c>
       <c r="AE49" s="7" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
-      <c r="A50" t="s">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A50" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="J50" s="5"/>
-      <c r="L50" s="6"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="5"/>
-      <c r="W50" s="6"/>
-      <c r="Z50" s="5"/>
-      <c r="AA50" s="6"/>
+      <c r="D50" s="11"/>
+      <c r="J50" s="6"/>
+      <c r="L50" s="11"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="6"/>
+      <c r="W50" s="11"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="11"/>
       <c r="AE50" s="7"/>
     </row>
-    <row r="51" spans="1:31">
-      <c r="A51" t="s">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A51" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
-      <c r="A52" t="s">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A52" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="O52" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="P52" s="4" t="s">
+      <c r="P52" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="R52" s="8" t="s">
+      <c r="R52" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="AC52" s="9" t="s">
+      <c r="AC52" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="AE52" s="9" t="s">
+      <c r="AE52" s="10" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="53" spans="1:31">
-      <c r="A53" t="s">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A53" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="7"/>
-      <c r="I53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="R53" s="8"/>
-      <c r="AC53" s="9"/>
-      <c r="AE53" s="9"/>
-    </row>
-    <row r="54" spans="1:31">
-      <c r="A54" t="s">
+      <c r="I53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="R53" s="9"/>
+      <c r="AC53" s="10"/>
+      <c r="AE53" s="10"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A54" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I54" s="9" t="s">
+      <c r="I54" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="O54" s="9" t="s">
+      <c r="O54" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="P54" s="9" t="s">
+      <c r="P54" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="R54" s="9" t="s">
+      <c r="R54" s="10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
-      <c r="A55" t="s">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
-      <c r="R55" s="9"/>
-    </row>
-    <row r="56" spans="1:31" s="2" customFormat="1">
-      <c r="A56" s="2" t="s">
+      <c r="I55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="R55" s="10"/>
+    </row>
+    <row r="56" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="11" t="s">
         <v>96</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K56" s="6" t="s">
+      <c r="K56" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="3" t="s">
+      <c r="M56" s="5" t="s">
         <v>131</v>
       </c>
       <c r="N56" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="8" t="s">
+      <c r="O56" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="P56" s="4" t="s">
+      <c r="P56" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="Q56" s="8" t="s">
+      <c r="Q56" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="R56" s="5" t="s">
+      <c r="R56" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="U56" s="9" t="s">
+      <c r="U56" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="W56" s="9" t="s">
+      <c r="W56" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="Y56" s="4" t="s">
+      <c r="Y56" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="Z56" s="4" t="s">
+      <c r="Z56" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="AA56" s="8" t="s">
+      <c r="AA56" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="AE56" s="4" t="s">
+      <c r="AE56" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="57" spans="1:31" s="2" customFormat="1">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C57" s="3"/>
-      <c r="I57" s="6"/>
+      <c r="C57" s="5"/>
+      <c r="I57" s="11"/>
       <c r="J57" s="7"/>
-      <c r="K57" s="6"/>
-      <c r="M57" s="3"/>
+      <c r="K57" s="11"/>
+      <c r="M57" s="5"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="5"/>
-      <c r="U57" s="9"/>
-      <c r="W57" s="9"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="8"/>
-      <c r="AE57" s="4"/>
-    </row>
-    <row r="58" spans="1:31" s="2" customFormat="1">
-      <c r="A58" s="2" t="s">
+      <c r="O57" s="9"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="6"/>
+      <c r="U57" s="10"/>
+      <c r="W57" s="10"/>
+      <c r="Y57" s="8"/>
+      <c r="Z57" s="8"/>
+      <c r="AA57" s="9"/>
+      <c r="AE57" s="8"/>
+    </row>
+    <row r="58" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="4" t="s">
+      <c r="K58" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="N58" s="5" t="s">
+      <c r="N58" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="P58" s="4" t="s">
+      <c r="P58" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="R58" s="8" t="s">
+      <c r="R58" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="S58" s="6" t="s">
+      <c r="S58" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="U58" s="3" t="s">
+      <c r="U58" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="W58" s="8" t="s">
+      <c r="W58" s="9" t="s">
         <v>301</v>
       </c>
       <c r="Y58" s="7" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="59" spans="1:31" s="2" customFormat="1">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="4"/>
-      <c r="N59" s="5"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="4"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="6"/>
-      <c r="U59" s="3"/>
-      <c r="W59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="8"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="11"/>
+      <c r="U59" s="5"/>
+      <c r="W59" s="9"/>
       <c r="Y59" s="7"/>
     </row>
-    <row r="60" spans="1:31" s="2" customFormat="1">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:31" s="2" customFormat="1">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="O61" s="5" t="s">
+      <c r="O61" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="P61" s="9" t="s">
+      <c r="P61" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="Q61" s="6" t="s">
+      <c r="Q61" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="R61" s="9" t="s">
+      <c r="R61" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="U61" s="5" t="s">
+      <c r="U61" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="Y61" s="5" t="s">
+      <c r="Y61" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="62" spans="1:31" s="2" customFormat="1">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I62" s="6"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="9"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="9"/>
-      <c r="U62" s="5"/>
-      <c r="Y62" s="5"/>
-    </row>
-    <row r="63" spans="1:31" s="2" customFormat="1">
-      <c r="A63" s="2" t="s">
+      <c r="I62" s="11"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="10"/>
+      <c r="U62" s="6"/>
+      <c r="Y62" s="6"/>
+    </row>
+    <row r="63" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O63" s="9" t="s">
+      <c r="O63" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="P63" s="9" t="s">
+      <c r="P63" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="R63" s="9" t="s">
+      <c r="R63" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:31" s="2" customFormat="1">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
-      <c r="R64" s="9"/>
-    </row>
-    <row r="65" spans="1:31">
-      <c r="A65" t="s">
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="R64" s="10"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A65" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O65" s="8" t="s">
+      <c r="O65" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P65" s="9" t="s">
+      <c r="P65" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="Q65" s="5" t="s">
+      <c r="Q65" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="R65" s="9" t="s">
+      <c r="R65" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="S65" s="3" t="s">
+      <c r="S65" s="5" t="s">
         <v>264</v>
       </c>
       <c r="V65" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="X65" s="6" t="s">
+      <c r="X65" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="AA65" s="8" t="s">
+      <c r="AA65" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="AC65" s="8" t="s">
+      <c r="AC65" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="AE65" s="8" t="s">
+      <c r="AE65" s="9" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
-      <c r="A66" t="s">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A66" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O66" s="8"/>
-      <c r="P66" s="9"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="9"/>
-      <c r="S66" s="3"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="5"/>
       <c r="V66" s="7"/>
-      <c r="X66" s="6"/>
-      <c r="AA66" s="8"/>
-      <c r="AC66" s="8"/>
-      <c r="AE66" s="8"/>
-    </row>
-    <row r="67" spans="1:31">
-      <c r="A67" t="s">
+      <c r="X66" s="11"/>
+      <c r="AA66" s="9"/>
+      <c r="AC66" s="9"/>
+      <c r="AE66" s="9"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A67" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="I67" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="O67" s="9" t="s">
+      <c r="O67" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="P67" s="9" t="s">
+      <c r="P67" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="R67" s="9" t="s">
+      <c r="R67" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="S67" s="5" t="s">
+      <c r="S67" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="U67" s="6" t="s">
+      <c r="U67" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="V67" s="9" t="s">
+      <c r="V67" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="AA67" s="4" t="s">
+      <c r="AA67" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AB67" s="4" t="s">
+      <c r="AB67" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="AC67" s="4" t="s">
+      <c r="AC67" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="AE67" s="4" t="s">
+      <c r="AE67" s="8" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
-      <c r="A68" t="s">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A68" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I68" s="4"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
-      <c r="R68" s="9"/>
-      <c r="S68" s="5"/>
-      <c r="U68" s="6"/>
-      <c r="V68" s="9"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AE68" s="4"/>
-    </row>
-    <row r="69" spans="1:31">
-      <c r="A69" t="s">
+      <c r="I68" s="8"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="6"/>
+      <c r="U68" s="11"/>
+      <c r="V68" s="10"/>
+      <c r="AA68" s="8"/>
+      <c r="AB68" s="8"/>
+      <c r="AC68" s="8"/>
+      <c r="AE68" s="8"/>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A69" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
-      <c r="A70" t="s">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A70" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I70" s="5" t="s">
+      <c r="I70" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="O70" s="5" t="s">
+      <c r="O70" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="P70" s="6" t="s">
+      <c r="P70" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="R70" s="9" t="s">
+      <c r="R70" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="X70" s="8" t="s">
+      <c r="X70" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="AA70" s="6" t="s">
+      <c r="AA70" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="AB70" s="4" t="s">
+      <c r="AB70" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="AC70" s="4" t="s">
+      <c r="AC70" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="AD70" s="4" t="s">
+      <c r="AD70" s="8" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
-      <c r="A71" t="s">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A71" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="6"/>
-      <c r="R71" s="9"/>
-      <c r="X71" s="8"/>
-      <c r="AA71" s="6"/>
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="4"/>
-      <c r="AD71" s="4"/>
-    </row>
-    <row r="72" spans="1:31">
-      <c r="A72" t="s">
+      <c r="I71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="11"/>
+      <c r="R71" s="10"/>
+      <c r="X71" s="9"/>
+      <c r="AA71" s="11"/>
+      <c r="AB71" s="8"/>
+      <c r="AC71" s="8"/>
+      <c r="AD71" s="8"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A72" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O72" s="5" t="s">
+      <c r="O72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="P72" s="5" t="s">
+      <c r="P72" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="Q72" s="5" t="s">
+      <c r="Q72" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="R72" s="6" t="s">
+      <c r="R72" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
-      <c r="A73" t="s">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A73" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O73" s="5"/>
-      <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
-      <c r="R73" s="6"/>
-    </row>
-    <row r="74" spans="1:31" s="2" customFormat="1">
-      <c r="A74" s="2" t="s">
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="11"/>
+    </row>
+    <row r="74" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I74" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="O74" s="5" t="s">
+      <c r="O74" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="P74" s="8" t="s">
+      <c r="P74" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="Q74" s="6" t="s">
+      <c r="Q74" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="R74" s="6" t="s">
+      <c r="R74" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="S74" s="5" t="s">
+      <c r="S74" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="T74" s="8" t="s">
+      <c r="T74" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="W74" s="6" t="s">
+      <c r="W74" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="Y74" s="5" t="s">
+      <c r="Y74" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="75" spans="1:31" s="2" customFormat="1">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E75" s="8"/>
-      <c r="I75" s="5"/>
+      <c r="E75" s="9"/>
+      <c r="I75" s="6"/>
       <c r="J75" s="7"/>
-      <c r="O75" s="5"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="5"/>
-      <c r="T75" s="8"/>
-      <c r="W75" s="6"/>
-      <c r="Y75" s="5"/>
-    </row>
-    <row r="76" spans="1:31" s="2" customFormat="1">
-      <c r="A76" s="2" t="s">
+      <c r="O75" s="6"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="6"/>
+      <c r="T75" s="9"/>
+      <c r="W75" s="11"/>
+      <c r="Y75" s="6"/>
+    </row>
+    <row r="76" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O76" s="6" t="s">
+      <c r="O76" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="P76" s="9" t="s">
+      <c r="P76" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="Q76" s="9" t="s">
+      <c r="Q76" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="R76" s="6" t="s">
+      <c r="R76" s="11" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:31" s="2" customFormat="1">
-      <c r="A77" s="2" t="s">
+    <row r="77" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D77" s="5"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="9"/>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="6"/>
-    </row>
-    <row r="78" spans="1:31" s="2" customFormat="1">
-      <c r="A78" s="2" t="s">
+      <c r="D77" s="6"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="11"/>
+    </row>
+    <row r="78" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:31" s="2" customFormat="1">
-      <c r="A79" s="2" t="s">
+    <row r="79" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O79" s="4" t="s">
+      <c r="O79" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="P79" s="9" t="s">
+      <c r="P79" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="Q79" s="4" t="s">
+      <c r="Q79" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="R79" s="9" t="s">
+      <c r="R79" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:31" s="2" customFormat="1">
-      <c r="A80" s="2" t="s">
+    <row r="80" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O80" s="4"/>
-      <c r="P80" s="9"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="9"/>
-    </row>
-    <row r="81" spans="1:31" s="2" customFormat="1">
-      <c r="A81" s="2" t="s">
+      <c r="O80" s="8"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="10"/>
+    </row>
+    <row r="81" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O81" s="5" t="s">
+      <c r="O81" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="P81" s="5" t="s">
+      <c r="P81" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="R81" s="6" t="s">
+      <c r="R81" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="AC81" s="4" t="s">
+      <c r="AC81" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="AE81" s="4" t="s">
+      <c r="AE81" s="8" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="82" spans="1:31" s="2" customFormat="1">
-      <c r="A82" s="2" t="s">
+    <row r="82" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="5"/>
-      <c r="P82" s="5"/>
-      <c r="R82" s="6"/>
-      <c r="AC82" s="4"/>
-      <c r="AE82" s="4"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6"/>
+      <c r="R82" s="11"/>
+      <c r="AC82" s="8"/>
+      <c r="AE82" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="358">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="A20:A28"/>
-    <mergeCell ref="A29:A37"/>
-    <mergeCell ref="A38:A46"/>
-    <mergeCell ref="A47:A55"/>
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="A65:A73"/>
-    <mergeCell ref="A74:A82"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="AE81:AE82"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AD29:AD30"/>
+    <mergeCell ref="AD44:AD45"/>
+    <mergeCell ref="AD70:AD71"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AE20:AE21"/>
+    <mergeCell ref="AE29:AE30"/>
+    <mergeCell ref="AE47:AE48"/>
+    <mergeCell ref="AE49:AE50"/>
+    <mergeCell ref="AE52:AE53"/>
+    <mergeCell ref="AE56:AE57"/>
+    <mergeCell ref="AE65:AE66"/>
+    <mergeCell ref="AE67:AE68"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="AC47:AC48"/>
+    <mergeCell ref="AC52:AC53"/>
+    <mergeCell ref="AC65:AC66"/>
+    <mergeCell ref="AC67:AC68"/>
+    <mergeCell ref="AC70:AC71"/>
+    <mergeCell ref="AC81:AC82"/>
+    <mergeCell ref="AA47:AA48"/>
+    <mergeCell ref="AA49:AA50"/>
+    <mergeCell ref="AA56:AA57"/>
+    <mergeCell ref="AA65:AA66"/>
+    <mergeCell ref="AA67:AA68"/>
+    <mergeCell ref="AA70:AA71"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AB20:AB21"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="AB67:AB68"/>
+    <mergeCell ref="AB70:AB71"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AA25:AA26"/>
+    <mergeCell ref="AA29:AA30"/>
+    <mergeCell ref="AA31:AA32"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="AA44:AA45"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="Y58:Y59"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="Y74:Y75"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="Z29:Z30"/>
+    <mergeCell ref="Z36:Z37"/>
+    <mergeCell ref="Z38:Z39"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Z56:Z57"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="Y29:Y30"/>
+    <mergeCell ref="Y36:Y37"/>
+    <mergeCell ref="Y38:Y39"/>
+    <mergeCell ref="Y44:Y45"/>
+    <mergeCell ref="W74:W75"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="X29:X30"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="X38:X39"/>
+    <mergeCell ref="X40:X41"/>
+    <mergeCell ref="X65:X66"/>
+    <mergeCell ref="X70:X71"/>
+    <mergeCell ref="V47:V48"/>
+    <mergeCell ref="V65:V66"/>
+    <mergeCell ref="V67:V68"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="W38:W39"/>
+    <mergeCell ref="W40:W41"/>
+    <mergeCell ref="W47:W48"/>
+    <mergeCell ref="W49:W50"/>
+    <mergeCell ref="W56:W57"/>
+    <mergeCell ref="W58:W59"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="V18:V19"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="V29:V30"/>
+    <mergeCell ref="V38:V39"/>
+    <mergeCell ref="V40:V41"/>
+    <mergeCell ref="V44:V45"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="U31:U32"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="U56:U57"/>
+    <mergeCell ref="U58:U59"/>
+    <mergeCell ref="U61:U62"/>
+    <mergeCell ref="U67:U68"/>
+    <mergeCell ref="R74:R75"/>
+    <mergeCell ref="R76:R77"/>
+    <mergeCell ref="R79:R80"/>
+    <mergeCell ref="R81:R82"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="S58:S59"/>
+    <mergeCell ref="S65:S66"/>
+    <mergeCell ref="S67:S68"/>
+    <mergeCell ref="S74:S75"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="R61:R62"/>
+    <mergeCell ref="R63:R64"/>
+    <mergeCell ref="R65:R66"/>
+    <mergeCell ref="R67:R68"/>
+    <mergeCell ref="R70:R71"/>
+    <mergeCell ref="R72:R73"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="Q76:Q77"/>
+    <mergeCell ref="Q79:Q80"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="R36:R37"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="R40:R41"/>
+    <mergeCell ref="R44:R45"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="R52:R53"/>
+    <mergeCell ref="P79:P80"/>
+    <mergeCell ref="P81:P82"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="Q36:Q37"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="Q44:Q45"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="Q56:Q57"/>
+    <mergeCell ref="Q61:Q62"/>
+    <mergeCell ref="Q65:Q66"/>
+    <mergeCell ref="Q72:Q73"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="P61:P62"/>
+    <mergeCell ref="P63:P64"/>
+    <mergeCell ref="P65:P66"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P70:P71"/>
+    <mergeCell ref="P72:P73"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="P76:P77"/>
+    <mergeCell ref="O81:O82"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="P44:P45"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="P52:P53"/>
+    <mergeCell ref="P54:P55"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="O61:O62"/>
+    <mergeCell ref="O63:O64"/>
+    <mergeCell ref="O65:O66"/>
+    <mergeCell ref="O67:O68"/>
+    <mergeCell ref="O70:O71"/>
+    <mergeCell ref="O72:O73"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="O76:O77"/>
+    <mergeCell ref="O79:O80"/>
     <mergeCell ref="N58:N59"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="O4:O5"/>
@@ -3597,232 +3755,114 @@
     <mergeCell ref="O54:O55"/>
     <mergeCell ref="O56:O57"/>
     <mergeCell ref="O58:O59"/>
-    <mergeCell ref="O61:O62"/>
-    <mergeCell ref="O63:O64"/>
-    <mergeCell ref="O65:O66"/>
-    <mergeCell ref="O67:O68"/>
-    <mergeCell ref="O70:O71"/>
-    <mergeCell ref="O72:O73"/>
-    <mergeCell ref="O74:O75"/>
-    <mergeCell ref="O76:O77"/>
-    <mergeCell ref="O79:O80"/>
-    <mergeCell ref="O81:O82"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="P40:P41"/>
-    <mergeCell ref="P44:P45"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="P49:P50"/>
-    <mergeCell ref="P52:P53"/>
-    <mergeCell ref="P54:P55"/>
-    <mergeCell ref="P56:P57"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="P61:P62"/>
-    <mergeCell ref="P63:P64"/>
-    <mergeCell ref="P65:P66"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P70:P71"/>
-    <mergeCell ref="P72:P73"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="P76:P77"/>
-    <mergeCell ref="P79:P80"/>
-    <mergeCell ref="P81:P82"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="Q49:Q50"/>
-    <mergeCell ref="Q56:Q57"/>
-    <mergeCell ref="Q61:Q62"/>
-    <mergeCell ref="Q65:Q66"/>
-    <mergeCell ref="Q72:Q73"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="Q76:Q77"/>
-    <mergeCell ref="Q79:Q80"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="R36:R37"/>
-    <mergeCell ref="R38:R39"/>
-    <mergeCell ref="R40:R41"/>
-    <mergeCell ref="R44:R45"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="R49:R50"/>
-    <mergeCell ref="R52:R53"/>
-    <mergeCell ref="R54:R55"/>
-    <mergeCell ref="R56:R57"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="R61:R62"/>
-    <mergeCell ref="R63:R64"/>
-    <mergeCell ref="R65:R66"/>
-    <mergeCell ref="R67:R68"/>
-    <mergeCell ref="R70:R71"/>
-    <mergeCell ref="R72:R73"/>
-    <mergeCell ref="R74:R75"/>
-    <mergeCell ref="R76:R77"/>
-    <mergeCell ref="R79:R80"/>
-    <mergeCell ref="R81:R82"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="S58:S59"/>
-    <mergeCell ref="S65:S66"/>
-    <mergeCell ref="S67:S68"/>
-    <mergeCell ref="S74:S75"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="T74:T75"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="U31:U32"/>
-    <mergeCell ref="U38:U39"/>
-    <mergeCell ref="U56:U57"/>
-    <mergeCell ref="U58:U59"/>
-    <mergeCell ref="U61:U62"/>
-    <mergeCell ref="U67:U68"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="V18:V19"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="V22:V23"/>
-    <mergeCell ref="V29:V30"/>
-    <mergeCell ref="V38:V39"/>
-    <mergeCell ref="V40:V41"/>
-    <mergeCell ref="V44:V45"/>
-    <mergeCell ref="V47:V48"/>
-    <mergeCell ref="V65:V66"/>
-    <mergeCell ref="V67:V68"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="W38:W39"/>
-    <mergeCell ref="W40:W41"/>
-    <mergeCell ref="W47:W48"/>
-    <mergeCell ref="W49:W50"/>
-    <mergeCell ref="W56:W57"/>
-    <mergeCell ref="W58:W59"/>
-    <mergeCell ref="W74:W75"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="X29:X30"/>
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X38:X39"/>
-    <mergeCell ref="X40:X41"/>
-    <mergeCell ref="X65:X66"/>
-    <mergeCell ref="X70:X71"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="Y29:Y30"/>
-    <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="Y38:Y39"/>
-    <mergeCell ref="Y44:Y45"/>
-    <mergeCell ref="Y47:Y48"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="Y58:Y59"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="Y74:Y75"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="Z29:Z30"/>
-    <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="Z38:Z39"/>
-    <mergeCell ref="Z49:Z50"/>
-    <mergeCell ref="Z56:Z57"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AA25:AA26"/>
-    <mergeCell ref="AA29:AA30"/>
-    <mergeCell ref="AA31:AA32"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="AA44:AA45"/>
-    <mergeCell ref="AA47:AA48"/>
-    <mergeCell ref="AA49:AA50"/>
-    <mergeCell ref="AA56:AA57"/>
-    <mergeCell ref="AA65:AA66"/>
-    <mergeCell ref="AA67:AA68"/>
-    <mergeCell ref="AA70:AA71"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AB20:AB21"/>
-    <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="AB67:AB68"/>
-    <mergeCell ref="AB70:AB71"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="AC47:AC48"/>
-    <mergeCell ref="AC52:AC53"/>
-    <mergeCell ref="AC65:AC66"/>
-    <mergeCell ref="AC67:AC68"/>
-    <mergeCell ref="AC70:AC71"/>
-    <mergeCell ref="AC81:AC82"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AD29:AD30"/>
-    <mergeCell ref="AD44:AD45"/>
-    <mergeCell ref="AD70:AD71"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AE20:AE21"/>
-    <mergeCell ref="AE29:AE30"/>
-    <mergeCell ref="AE47:AE48"/>
-    <mergeCell ref="AE49:AE50"/>
-    <mergeCell ref="AE52:AE53"/>
-    <mergeCell ref="AE56:AE57"/>
-    <mergeCell ref="AE65:AE66"/>
-    <mergeCell ref="AE67:AE68"/>
-    <mergeCell ref="AE81:AE82"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="A29:A37"/>
+    <mergeCell ref="A38:A46"/>
+    <mergeCell ref="A47:A55"/>
+    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="A65:A73"/>
+    <mergeCell ref="A74:A82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/runs/exp8_final/beautified_exam_schedule.xlsx
+++ b/runs/exp8_final/beautified_exam_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/runs/exp8_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_42655B9F120D3DDA63169890BF2B360379785166" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0892399E-0454-40C7-9193-60E60CC0DFB8}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_42655B9F120D3DDA63169890BF2B360379785166" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{820ABAD1-FA97-43D4-A302-51F3AC9AEEC3}"/>
   <bookViews>
-    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -1279,6 +1279,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1290,9 +1293,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1308,6 +1308,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1698,1814 +1702,1814 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AF1" s="3" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="9" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="6"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="10"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="11"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="5"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="7"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="11"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="12"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="6"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
     </row>
     <row r="4" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="W4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="X4" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="Y4" s="11" t="s">
+      <c r="Y4" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="AA4" s="10" t="s">
+      <c r="AA4" s="11" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="10"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="11"/>
-      <c r="AA5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="11"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="12"/>
+      <c r="AA5" s="11"/>
     </row>
     <row r="6" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="Q7" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="R7" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="U7" s="10" t="s">
+      <c r="U7" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" s="6" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="G8" s="6"/>
-      <c r="L8" s="11"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="11"/>
-      <c r="U8" s="10"/>
-      <c r="X8" s="5"/>
+      <c r="E8" s="11"/>
+      <c r="G8" s="7"/>
+      <c r="L8" s="12"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="12"/>
+      <c r="U8" s="11"/>
+      <c r="X8" s="6"/>
     </row>
     <row r="9" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="S9" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="U9" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="AA9" s="6" t="s">
+      <c r="AA9" s="7" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="AA10" s="6"/>
+      <c r="I10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="AA10" s="7"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="R11" s="7" t="s">
+      <c r="R11" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="T11" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="U11" s="5" t="s">
+      <c r="U11" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="V11" s="7" t="s">
+      <c r="V11" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="X11" s="5" t="s">
+      <c r="X11" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y11" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="Z11" s="5" t="s">
+      <c r="Z11" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="AA11" s="7" t="s">
+      <c r="AA11" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="AD11" s="7" t="s">
+      <c r="AD11" s="8" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="5"/>
-      <c r="G12" s="6" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="6"/>
+      <c r="G12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="7"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="7"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="7"/>
-      <c r="AD12" s="7"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="9"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="8"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="8"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="8"/>
+      <c r="AD12" s="8"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="I13" s="10" t="s">
+      <c r="G13" s="7"/>
+      <c r="I13" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" s="10" t="s">
+      <c r="Q13" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="R13" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="V13" s="11" t="s">
+      <c r="V13" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="Y13" s="11" t="s">
+      <c r="Y13" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="Z13" s="8" t="s">
+      <c r="Z13" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="7"/>
-      <c r="V14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="I14" s="11"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="8"/>
+      <c r="V14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="O16" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="7" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
+      <c r="I17" s="10"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="Q18" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="R18" s="8" t="s">
+      <c r="R18" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="V18" s="8" t="s">
+      <c r="V18" s="9" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="V19" s="8"/>
+      <c r="I19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="V19" s="9"/>
     </row>
     <row r="20" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="N20" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="O20" s="10" t="s">
+      <c r="O20" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="P20" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="Q20" s="9" t="s">
+      <c r="Q20" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="R20" s="6" t="s">
+      <c r="R20" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="T20" s="5" t="s">
+      <c r="T20" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="U20" s="7" t="s">
+      <c r="U20" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="V20" s="9" t="s">
+      <c r="V20" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="W20" s="7" t="s">
+      <c r="W20" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="X20" s="10" t="s">
+      <c r="X20" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="AA20" s="5" t="s">
+      <c r="AA20" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="AB20" s="8" t="s">
+      <c r="AB20" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="AC20" s="8" t="s">
+      <c r="AC20" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="AE20" s="8" t="s">
+      <c r="AE20" s="9" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="5"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="6"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="10"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AE21" s="8"/>
+      <c r="E21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="K21" s="6"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="7"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="11"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AE21" s="9"/>
     </row>
     <row r="22" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="O22" s="6" t="s">
+      <c r="O22" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="P22" s="11" t="s">
+      <c r="P22" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="Q22" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="R22" s="6" t="s">
+      <c r="R22" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="U22" s="9" t="s">
+      <c r="U22" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="V22" s="9" t="s">
+      <c r="V22" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="AB22" s="8" t="s">
+      <c r="AB22" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="AC22" s="8" t="s">
+      <c r="AC22" s="9" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="7"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="7"/>
+      <c r="K23" s="8"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
     </row>
     <row r="24" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="N25" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P25" s="8" t="s">
+      <c r="P25" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="Q25" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="R25" s="11" t="s">
+      <c r="R25" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="AA25" s="6" t="s">
+      <c r="AA25" s="7" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="K26" s="11"/>
-      <c r="N26" s="9"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="AA26" s="6"/>
+      <c r="I26" s="9"/>
+      <c r="K26" s="12"/>
+      <c r="N26" s="10"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="AA26" s="7"/>
     </row>
     <row r="27" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="N27" s="10" t="s">
+      <c r="N27" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="O27" s="10" t="s">
+      <c r="O27" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="P27" s="10" t="s">
+      <c r="P27" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="R27" s="10" t="s">
+      <c r="R27" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="Y27" s="7" t="s">
+      <c r="Y27" s="8" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="Y28" s="7"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="Y28" s="8"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="M29" s="9" t="s">
+      <c r="M29" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="O29" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="P29" s="9" t="s">
+      <c r="P29" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="Q29" s="10" t="s">
+      <c r="Q29" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="R29" s="11" t="s">
+      <c r="R29" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="S29" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="T29" s="7" t="s">
+      <c r="T29" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="V29" s="7" t="s">
+      <c r="V29" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="X29" s="9" t="s">
+      <c r="X29" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="Y29" s="9" t="s">
+      <c r="Y29" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="Z29" s="5" t="s">
+      <c r="Z29" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="AA29" s="5" t="s">
+      <c r="AA29" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="AD29" s="8" t="s">
+      <c r="AC29" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="AD29" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="AE29" s="8" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="10"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="5"/>
-      <c r="I30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="5"/>
-      <c r="AA30" s="5"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="8"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="11"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="6"/>
+      <c r="I30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="P31" s="10" t="s">
+      <c r="P31" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="R31" s="10" t="s">
+      <c r="R31" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="U31" s="11" t="s">
+      <c r="U31" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="AA31" s="10" t="s">
+      <c r="AA31" s="11" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="D32" s="10"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="U32" s="11"/>
-      <c r="AA32" s="10"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A33" s="4" t="s">
+      <c r="B32" s="7"/>
+      <c r="D32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="U32" s="12"/>
+      <c r="AA32" s="11"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A33" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="O36" s="6" t="s">
+      <c r="O36" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P36" s="6" t="s">
+      <c r="P36" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="Q36" s="11" t="s">
+      <c r="Q36" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="R36" s="9" t="s">
+      <c r="R36" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="X36" s="6" t="s">
+      <c r="X36" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="Y36" s="10" t="s">
+      <c r="Y36" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="Z36" s="11" t="s">
+      <c r="Z36" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="AA36" s="11" t="s">
+      <c r="AA36" s="12" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="9"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="11"/>
-      <c r="AA37" s="11"/>
-    </row>
-    <row r="38" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="3" t="s">
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="10"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="12"/>
+    </row>
+    <row r="38" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="L38" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="O38" s="10" t="s">
+      <c r="O38" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="P38" s="10" t="s">
+      <c r="P38" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="Q38" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="R38" s="10" t="s">
+      <c r="R38" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="U38" s="9" t="s">
+      <c r="U38" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="V38" s="9" t="s">
+      <c r="V38" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="W38" s="9" t="s">
+      <c r="W38" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="X38" s="7" t="s">
+      <c r="X38" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="Y38" s="11" t="s">
+      <c r="Y38" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="Z38" s="5" t="s">
+      <c r="Z38" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="F39" s="9"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="9"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="11"/>
-      <c r="Z39" s="5"/>
-    </row>
-    <row r="40" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="3" t="s">
+      <c r="B39" s="8"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="F39" s="10"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="10"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="8"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="6"/>
+    </row>
+    <row r="40" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="O40" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="P40" s="5" t="s">
+      <c r="P40" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="Q40" s="11" t="s">
+      <c r="Q40" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="R40" s="8" t="s">
+      <c r="R40" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="V40" s="8" t="s">
+      <c r="V40" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="W40" s="5" t="s">
+      <c r="W40" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="X40" s="7" t="s">
+      <c r="X40" s="8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="I41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="5"/>
-      <c r="X41" s="7"/>
-    </row>
-    <row r="42" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="3" t="s">
+      <c r="D41" s="12"/>
+      <c r="I41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="7"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="8"/>
+    </row>
+    <row r="42" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="10" t="s">
+      <c r="L44" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="P44" s="10" t="s">
+      <c r="P44" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="Q44" s="10" t="s">
+      <c r="Q44" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="R44" s="11" t="s">
+      <c r="R44" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="V44" s="10" t="s">
+      <c r="V44" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="Y44" s="10" t="s">
+      <c r="Y44" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="AA44" s="6" t="s">
+      <c r="AA44" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="AD44" s="6" t="s">
+      <c r="AD44" s="7" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="6"/>
-      <c r="L45" s="10"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="11"/>
-      <c r="V45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="AA45" s="6"/>
-      <c r="AD45" s="6"/>
-    </row>
-    <row r="46" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="3" t="s">
+      <c r="C45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="7"/>
+      <c r="L45" s="11"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="12"/>
+      <c r="V45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="AA45" s="7"/>
+      <c r="AD45" s="7"/>
+    </row>
+    <row r="46" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="H47" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="O47" s="6" t="s">
+      <c r="O47" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="P47" s="9" t="s">
+      <c r="P47" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="Q47" s="5" t="s">
+      <c r="Q47" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="R47" s="9" t="s">
+      <c r="R47" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="V47" s="7" t="s">
+      <c r="V47" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="W47" s="5" t="s">
+      <c r="W47" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="Y47" s="11" t="s">
+      <c r="Y47" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="AA47" s="6" t="s">
+      <c r="AA47" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="AC47" s="8" t="s">
+      <c r="AB47" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="AC47" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="AE47" s="8" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A48" s="4" t="s">
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A48" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="11"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="7"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="9"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="5"/>
-      <c r="Y48" s="11"/>
-      <c r="AA48" s="6"/>
-      <c r="AC48" s="8"/>
-      <c r="AE48" s="8"/>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A49" s="4" t="s">
+      <c r="F48" s="12"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="8"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="10"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="6"/>
+      <c r="Y48" s="12"/>
+      <c r="AA48" s="7"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A49" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="J49" s="6" t="s">
+      <c r="J49" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="P49" s="10" t="s">
+      <c r="P49" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="Q49" s="10" t="s">
+      <c r="Q49" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="R49" s="6" t="s">
+      <c r="R49" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="W49" s="11" t="s">
+      <c r="W49" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="Z49" s="6" t="s">
+      <c r="Z49" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="AA49" s="11" t="s">
+      <c r="AA49" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="AE49" s="7" t="s">
+      <c r="AB49" s="8" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A50" s="4" t="s">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A50" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="J50" s="6"/>
-      <c r="L50" s="11"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="6"/>
-      <c r="W50" s="11"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="11"/>
-      <c r="AE50" s="7"/>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A51" s="4" t="s">
+      <c r="D50" s="12"/>
+      <c r="J50" s="7"/>
+      <c r="L50" s="12"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="7"/>
+      <c r="W50" s="12"/>
+      <c r="Z50" s="7"/>
+      <c r="AA50" s="12"/>
+      <c r="AB50" s="8"/>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A51" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A52" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="O52" s="8" t="s">
+      <c r="O52" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="P52" s="8" t="s">
+      <c r="P52" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="R52" s="9" t="s">
+      <c r="R52" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="AC52" s="10" t="s">
+      <c r="AB52" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC52" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="AE52" s="10" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A53" s="4" t="s">
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A53" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="7"/>
-      <c r="I53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="R53" s="9"/>
-      <c r="AC53" s="10"/>
-      <c r="AE53" s="10"/>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A54" s="4" t="s">
+      <c r="D53" s="8"/>
+      <c r="I53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="R53" s="10"/>
+      <c r="AB53" s="11"/>
+      <c r="AC53" s="11"/>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A54" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="O54" s="10" t="s">
+      <c r="O54" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="P54" s="10" t="s">
+      <c r="P54" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="R54" s="10" t="s">
+      <c r="R54" s="11" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A55" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="R55" s="10"/>
-    </row>
-    <row r="56" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="3" t="s">
+      <c r="I55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="R55" s="11"/>
+    </row>
+    <row r="56" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J56" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="M56" s="5" t="s">
+      <c r="M56" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="N56" s="7" t="s">
+      <c r="N56" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="9" t="s">
+      <c r="O56" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="P56" s="8" t="s">
+      <c r="P56" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="Q56" s="9" t="s">
+      <c r="Q56" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="R56" s="6" t="s">
+      <c r="R56" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="U56" s="10" t="s">
+      <c r="U56" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="W56" s="10" t="s">
+      <c r="W56" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="Y56" s="8" t="s">
+      <c r="Y56" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="Z56" s="8" t="s">
+      <c r="Z56" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="AA56" s="9" t="s">
+      <c r="AA56" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="AE56" s="8" t="s">
+      <c r="AC56" s="9" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="57" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="11"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="7"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="6"/>
-      <c r="U57" s="10"/>
-      <c r="W57" s="10"/>
-      <c r="Y57" s="8"/>
-      <c r="Z57" s="8"/>
-      <c r="AA57" s="9"/>
-      <c r="AE57" s="8"/>
-    </row>
-    <row r="58" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="3" t="s">
+      <c r="C57" s="6"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="12"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="7"/>
+      <c r="U57" s="11"/>
+      <c r="W57" s="11"/>
+      <c r="Y57" s="9"/>
+      <c r="Z57" s="9"/>
+      <c r="AA57" s="10"/>
+      <c r="AC57" s="9"/>
+    </row>
+    <row r="58" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="8" t="s">
+      <c r="K58" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="N58" s="6" t="s">
+      <c r="N58" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="O58" s="5" t="s">
+      <c r="O58" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="P58" s="8" t="s">
+      <c r="P58" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="R58" s="9" t="s">
+      <c r="R58" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="S58" s="11" t="s">
+      <c r="S58" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="U58" s="5" t="s">
+      <c r="U58" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="W58" s="9" t="s">
+      <c r="W58" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="Y58" s="7" t="s">
+      <c r="Y58" s="8" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="59" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="3" t="s">
+    <row r="59" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K59" s="8"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="5"/>
-      <c r="P59" s="8"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="11"/>
-      <c r="U59" s="5"/>
-      <c r="W59" s="9"/>
-      <c r="Y59" s="7"/>
-    </row>
-    <row r="60" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="3" t="s">
+      <c r="K59" s="9"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="9"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="12"/>
+      <c r="U59" s="6"/>
+      <c r="W59" s="10"/>
+      <c r="Y59" s="8"/>
+    </row>
+    <row r="60" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="3" t="s">
+    <row r="61" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="O61" s="6" t="s">
+      <c r="O61" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="P61" s="10" t="s">
+      <c r="P61" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="Q61" s="11" t="s">
+      <c r="Q61" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="R61" s="10" t="s">
+      <c r="R61" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="U61" s="6" t="s">
+      <c r="U61" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="Y61" s="6" t="s">
+      <c r="Y61" s="7" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="62" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="3" t="s">
+    <row r="62" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I62" s="11"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="11"/>
-      <c r="R62" s="10"/>
-      <c r="U62" s="6"/>
-      <c r="Y62" s="6"/>
-    </row>
-    <row r="63" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="3" t="s">
+      <c r="I62" s="12"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="11"/>
+      <c r="U62" s="7"/>
+      <c r="Y62" s="7"/>
+    </row>
+    <row r="63" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="O63" s="10" t="s">
+      <c r="O63" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="P63" s="10" t="s">
+      <c r="P63" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="R63" s="10" t="s">
+      <c r="R63" s="11" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="R64" s="10"/>
-    </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A65" s="4" t="s">
+      <c r="O64" s="11"/>
+      <c r="P64" s="11"/>
+      <c r="R64" s="11"/>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O65" s="9" t="s">
+      <c r="O65" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="P65" s="10" t="s">
+      <c r="P65" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="Q65" s="6" t="s">
+      <c r="Q65" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="R65" s="10" t="s">
+      <c r="R65" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="S65" s="5" t="s">
+      <c r="S65" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="V65" s="7" t="s">
+      <c r="V65" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="X65" s="11" t="s">
+      <c r="X65" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="AA65" s="9" t="s">
+      <c r="AA65" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="AC65" s="9" t="s">
+      <c r="AB65" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AC65" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="AE65" s="9" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A66" s="4" t="s">
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A66" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O66" s="9"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="10"/>
-      <c r="S66" s="5"/>
-      <c r="V66" s="7"/>
-      <c r="X66" s="11"/>
-      <c r="AA66" s="9"/>
-      <c r="AC66" s="9"/>
-      <c r="AE66" s="9"/>
-    </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A67" s="4" t="s">
+      <c r="O66" s="10"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="7"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="6"/>
+      <c r="V66" s="8"/>
+      <c r="X66" s="12"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="10"/>
+      <c r="AC66" s="10"/>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="O67" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="P67" s="10" t="s">
+      <c r="P67" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="R67" s="10" t="s">
+      <c r="R67" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="S67" s="6" t="s">
+      <c r="S67" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="U67" s="11" t="s">
+      <c r="U67" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="V67" s="10" t="s">
+      <c r="V67" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="AA67" s="8" t="s">
+      <c r="AA67" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="AB67" s="8" t="s">
+      <c r="AB67" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="AC67" s="8" t="s">
+      <c r="AC67" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="AD67" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="AE67" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A68" s="4" t="s">
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A68" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I68" s="8"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="6"/>
-      <c r="U68" s="11"/>
-      <c r="V68" s="10"/>
-      <c r="AA68" s="8"/>
-      <c r="AB68" s="8"/>
-      <c r="AC68" s="8"/>
-      <c r="AE68" s="8"/>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A69" s="4" t="s">
+      <c r="I68" s="9"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="11"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="7"/>
+      <c r="U68" s="12"/>
+      <c r="V68" s="11"/>
+      <c r="AA68" s="9"/>
+      <c r="AB68" s="9"/>
+      <c r="AC68" s="9"/>
+      <c r="AD68" s="9"/>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A69" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A70" s="4" t="s">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A70" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I70" s="6" t="s">
+      <c r="I70" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O70" s="6" t="s">
+      <c r="O70" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="P70" s="11" t="s">
+      <c r="P70" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="R70" s="10" t="s">
+      <c r="R70" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="X70" s="9" t="s">
+      <c r="X70" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="AA70" s="11" t="s">
+      <c r="AA70" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="AB70" s="8" t="s">
+      <c r="AB70" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="AC70" s="8" t="s">
+      <c r="AC70" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="AD70" s="8" t="s">
+      <c r="AD70" s="9" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A71" s="4" t="s">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A71" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="11"/>
-      <c r="R71" s="10"/>
-      <c r="X71" s="9"/>
-      <c r="AA71" s="11"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-    </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A72" s="4" t="s">
+      <c r="I71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="12"/>
+      <c r="R71" s="11"/>
+      <c r="X71" s="10"/>
+      <c r="AA71" s="12"/>
+      <c r="AB71" s="9"/>
+      <c r="AC71" s="9"/>
+      <c r="AD71" s="9"/>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A72" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O72" s="6" t="s">
+      <c r="O72" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="P72" s="6" t="s">
+      <c r="P72" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="Q72" s="6" t="s">
+      <c r="Q72" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="R72" s="11" t="s">
+      <c r="R72" s="12" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A73" s="4" t="s">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="11"/>
-    </row>
-    <row r="74" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="3" t="s">
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="12"/>
+    </row>
+    <row r="74" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="I74" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J74" s="7" t="s">
+      <c r="J74" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="O74" s="6" t="s">
+      <c r="O74" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="P74" s="9" t="s">
+      <c r="P74" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="Q74" s="11" t="s">
+      <c r="Q74" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="R74" s="11" t="s">
+      <c r="R74" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="S74" s="6" t="s">
+      <c r="S74" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="T74" s="9" t="s">
+      <c r="T74" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="W74" s="11" t="s">
+      <c r="W74" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="Y74" s="6" t="s">
+      <c r="Y74" s="7" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="75" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="7"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="9"/>
-      <c r="Q75" s="11"/>
-      <c r="R75" s="11"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="9"/>
-      <c r="W75" s="11"/>
-      <c r="Y75" s="6"/>
-    </row>
-    <row r="76" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="3" t="s">
+      <c r="E75" s="10"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="8"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="12"/>
+      <c r="R75" s="12"/>
+      <c r="S75" s="7"/>
+      <c r="T75" s="10"/>
+      <c r="W75" s="12"/>
+      <c r="Y75" s="7"/>
+    </row>
+    <row r="76" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="P76" s="10" t="s">
+      <c r="P76" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="Q76" s="10" t="s">
+      <c r="Q76" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="R76" s="11" t="s">
+      <c r="R76" s="12" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D77" s="6"/>
-      <c r="O77" s="11"/>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="11"/>
-    </row>
-    <row r="78" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="3" t="s">
+      <c r="D77" s="7"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="11"/>
+      <c r="Q77" s="11"/>
+      <c r="R77" s="12"/>
+    </row>
+    <row r="78" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O79" s="8" t="s">
+      <c r="O79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="P79" s="10" t="s">
+      <c r="P79" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="Q79" s="8" t="s">
+      <c r="Q79" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="R79" s="10" t="s">
+      <c r="R79" s="11" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O80" s="8"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="10"/>
-    </row>
-    <row r="81" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="3" t="s">
+      <c r="O80" s="9"/>
+      <c r="P80" s="11"/>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="11"/>
+    </row>
+    <row r="81" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O81" s="6" t="s">
+      <c r="O81" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="P81" s="6" t="s">
+      <c r="P81" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="R81" s="11" t="s">
+      <c r="R81" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="AC81" s="8" t="s">
+      <c r="AB81" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC81" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="AE81" s="8" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="3" t="s">
+    </row>
+    <row r="82" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="6"/>
-      <c r="P82" s="6"/>
-      <c r="R82" s="11"/>
-      <c r="AC82" s="8"/>
-      <c r="AE82" s="8"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+      <c r="R82" s="12"/>
+      <c r="AB82" s="9"/>
+      <c r="AC82" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="358">
-    <mergeCell ref="AE81:AE82"/>
+    <mergeCell ref="AB81:AB82"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AD29:AD30"/>
@@ -3513,20 +3517,20 @@
     <mergeCell ref="AD70:AD71"/>
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AE20:AE21"/>
-    <mergeCell ref="AE29:AE30"/>
-    <mergeCell ref="AE47:AE48"/>
-    <mergeCell ref="AE49:AE50"/>
-    <mergeCell ref="AE52:AE53"/>
-    <mergeCell ref="AE56:AE57"/>
-    <mergeCell ref="AE65:AE66"/>
-    <mergeCell ref="AE67:AE68"/>
+    <mergeCell ref="AC29:AC30"/>
+    <mergeCell ref="AB47:AB48"/>
+    <mergeCell ref="AB49:AB50"/>
+    <mergeCell ref="AB52:AB53"/>
+    <mergeCell ref="AC56:AC57"/>
+    <mergeCell ref="AB65:AB66"/>
+    <mergeCell ref="AC67:AC68"/>
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="AC20:AC21"/>
     <mergeCell ref="AC22:AC23"/>
     <mergeCell ref="AC47:AC48"/>
     <mergeCell ref="AC52:AC53"/>
     <mergeCell ref="AC65:AC66"/>
-    <mergeCell ref="AC67:AC68"/>
+    <mergeCell ref="AD67:AD68"/>
     <mergeCell ref="AC70:AC71"/>
     <mergeCell ref="AC81:AC82"/>
     <mergeCell ref="AA47:AA48"/>
